--- a/ESPacc development.xlsx
+++ b/ESPacc development.xlsx
@@ -1,31 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\Arduino\ESPaccessoryController\ESPaccessoryController\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F81D498A-D7ED-4DCF-94BE-48A886FEBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E602F1-DE52-4770-84C4-26E957A47040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Panel Pro LoconetServer" sheetId="1" r:id="rId1"/>
+    <sheet name="comms flows" sheetId="2" r:id="rId2"/>
+    <sheet name="non DCC_ESP system" sheetId="5" r:id="rId3"/>
+    <sheet name="tests" sheetId="3" r:id="rId4"/>
+    <sheet name="modes" sheetId="4" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="375">
   <si>
     <t>Currently the ACC_ESP supports</t>
   </si>
@@ -478,13 +492,685 @@
   </si>
   <si>
     <t>[B2 09 50 14]  Sensor LS19 (test19) is High</t>
+  </si>
+  <si>
+    <t>Multiple ESPACC devices.</t>
+  </si>
+  <si>
+    <t>Here are the message flows</t>
+  </si>
+  <si>
+    <t>Have one set up as the LN server running port 1234  Another as a LN client connecting  to port 4234.</t>
+  </si>
+  <si>
+    <t>turnout 7 thrown</t>
+  </si>
+  <si>
+    <t>[B0 06 10 59]  Requesting Switch at LT7 to Thrown (Output On).</t>
+  </si>
+  <si>
+    <t>[B0 06 00 49]  Requesting Switch at LT7 to Thrown (Output Off).</t>
+  </si>
+  <si>
+    <t>On the LN server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">it is doing its thing we are not </t>
+  </si>
+  <si>
+    <t>monitoring its serial port</t>
+  </si>
+  <si>
+    <t>On the ESPACC client</t>
+  </si>
+  <si>
+    <t>IN: RECEIVE B0 06 10 59</t>
+  </si>
+  <si>
+    <t>Turnout 7 thrown</t>
+  </si>
+  <si>
+    <t>IN: RECEIVE B0 06 00 49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My laptop is </t>
+  </si>
+  <si>
+    <t>HP-Ultra-5.local</t>
+  </si>
+  <si>
+    <t>on  Hercules client HP-Ultra-5.local:4234</t>
+  </si>
+  <si>
+    <t>RECEIVE B0 06 10 59</t>
+  </si>
+  <si>
+    <t>RECEIVE B0 06 00 49</t>
+  </si>
+  <si>
+    <t>this also sends out ESPACC as a heartbeat</t>
+  </si>
+  <si>
+    <t>but JRMI port 4234 does not re-broadcast this</t>
+  </si>
+  <si>
+    <t>OK so lets try an event on the client</t>
+  </si>
+  <si>
+    <t>OUT: SEND B2 00 60 2D</t>
+  </si>
+  <si>
+    <t>IN: RECEIVE B2 00 60 2D</t>
+  </si>
+  <si>
+    <t>OUT: SEND B2 00 70 3D</t>
+  </si>
+  <si>
+    <t>IN: RECEIVE B2 00 70 3D</t>
+  </si>
+  <si>
+    <t>OUT: ESPACC</t>
+  </si>
+  <si>
+    <t>LN server processed it</t>
+  </si>
+  <si>
+    <t>hence the RECEIVE messages</t>
+  </si>
+  <si>
+    <t>So the unexpected behaviour here is on the client.  It hosts sensor 2</t>
+  </si>
+  <si>
+    <t>if we send this, nothing happens.  The LN server does nothing with it</t>
+  </si>
+  <si>
+    <t>and it is not relayed by the LN server to the other clients.</t>
+  </si>
+  <si>
+    <t>If instead we report a state with SEND</t>
+  </si>
+  <si>
+    <t>LN server processes it</t>
+  </si>
+  <si>
+    <t>but ultimately the device hosting the pin correctly reports its state</t>
+  </si>
+  <si>
+    <t>from LN server &gt;&gt;&gt;</t>
+  </si>
+  <si>
+    <t>It raises an event as SEND, and the LN server echos the same event data as RECEIVE followed by SEND OK.  These came back to the client.</t>
+  </si>
+  <si>
+    <t>The client itself is in theory capable of responding to RECEIVE as an input, but it does not respond here. Why?  I had expected it to.</t>
+  </si>
+  <si>
+    <t>Now a query event from JRMI PP</t>
+  </si>
+  <si>
+    <t>PP polls assuming sensor is low but this is our client</t>
+  </si>
+  <si>
+    <t>&gt;&gt;</t>
+  </si>
+  <si>
+    <t>responding to a RECEIVE message from LN server</t>
+  </si>
+  <si>
+    <t>our client sends the actual status it has, which is hi&gt;&gt;&gt;</t>
+  </si>
+  <si>
+    <t>and the LN controller receives and processes</t>
+  </si>
+  <si>
+    <t>this with an OK</t>
+  </si>
+  <si>
+    <t>&lt;&lt;&lt; from PP</t>
+  </si>
+  <si>
+    <t>&lt;&lt; from ESP_ACC client</t>
+  </si>
+  <si>
+    <t>Maybe our device wants to process that RECEIVE message but the outbound</t>
+  </si>
+  <si>
+    <t>message queue has monopolised transmission</t>
+  </si>
+  <si>
+    <t>sent from Hercules</t>
+  </si>
+  <si>
+    <t>from LN controller as echo</t>
+  </si>
+  <si>
+    <t>from LN controller as echo / ok</t>
+  </si>
+  <si>
+    <t>&lt;&lt;</t>
+  </si>
+  <si>
+    <t>To LN controller</t>
+  </si>
+  <si>
+    <t>LN controller response</t>
+  </si>
+  <si>
+    <t>goes over broadcast</t>
+  </si>
+  <si>
+    <t>client responds to broadcast by sending the port state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;&lt;&lt; but yeah the device does not respond to the exact same RECEIVE command. </t>
+  </si>
+  <si>
+    <t>it does not cause a qry sensor 2 trigger.</t>
+  </si>
+  <si>
+    <t>IN: RECEIVE ED 0B 7F 32 01 05 73 05 00 00 26</t>
+  </si>
+  <si>
+    <t>MAS 22 05</t>
+  </si>
+  <si>
+    <t>OUT: RECEIVE 0xB4 0x7D 0x7F 0x49</t>
+  </si>
+  <si>
+    <t>[ED 0B 7F 32 01 05 73 05 00 00 26]  Extended Accessory Decoder Set Digitrax Address 22 (NMRA Address 18) to Aspect 5.</t>
+  </si>
+  <si>
+    <t>IN: RECEIVE ED 0B 7F 32 01 05 73 1F 00 00 3C</t>
+  </si>
+  <si>
+    <t>MAS 22 1F</t>
+  </si>
+  <si>
+    <t>[ED 0B 7F 32 01 05 73 1F 00 00 3C]  Extended Accessory Decoder Set Digitrax Address 22 (NMRA Address 18) to Aspect 31.</t>
+  </si>
+  <si>
+    <t>I think this is a standard 4 byte ack message for MAS</t>
+  </si>
+  <si>
+    <t>In Conclusion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We do not need a client mode that connects specially with the ESP_DCC.  </t>
+  </si>
+  <si>
+    <t>If you do accidentally connect direct to the ESP_DCC then it will still work.</t>
+  </si>
+  <si>
+    <t>And we seem to be ok with host/client mode on the ESP_ACC as written.</t>
+  </si>
+  <si>
+    <t>now for one more test, which is to see if the sensor client still works properly and reports to JRMI if we ask Herc to connect to it.  I never designed it to answer multiple connections</t>
+  </si>
+  <si>
+    <t>Actually the client will give you error TCP connection error :10061</t>
+  </si>
+  <si>
+    <t>This is because it is acting as a client on port 4234 and its therefore not listening and not ready to connect to a client.   That's ok.</t>
+  </si>
+  <si>
+    <t>You could possibly conect to the LN controller.</t>
+  </si>
+  <si>
+    <t>Yeah you can connect and it does seem to bugger up the LN controller.  So don't do it!  Perhaps we can make the LN controller refuse a second+ connection.</t>
+  </si>
+  <si>
+    <t>JMRI communicates using loconet over tcp which adds extra wrappers</t>
+  </si>
+  <si>
+    <t>SEND payload &gt;&gt;</t>
+  </si>
+  <si>
+    <t>&lt;&lt; receive payload</t>
+  </si>
+  <si>
+    <t>&lt;&lt; SENT OK</t>
+  </si>
+  <si>
+    <t>and async sensor messages are</t>
+  </si>
+  <si>
+    <t>ACC_ESP client acts only on the receive messages, and only these are</t>
+  </si>
+  <si>
+    <t>ACC_ESP client also raises SEND for sensor events</t>
+  </si>
+  <si>
+    <t>Conclusion:</t>
+  </si>
+  <si>
+    <t>DCC_ESP can actually echo the same LN responses to ACC_ESP as the ACC_ESP client will only act on the RECEIVE payload message</t>
+  </si>
+  <si>
+    <t>If the client needs to raise a sensor event, it issues a SEND message.   DCC_ESP must act on this by echoing it out to clients as Receive / sent ok.</t>
+  </si>
+  <si>
+    <t>so there actually is no difference between a JMRI client other than it issues send commands.</t>
+  </si>
+  <si>
+    <t>sent to it over JMRI loconet server.  It consumes these with no response. Exception is a sensor poll.</t>
+  </si>
+  <si>
+    <t>How does DCC_ESP detect the LN client?  If SEND is present.   ACC_ESP won't send this, so I think its ok we just work with the "ACCESP" message</t>
+  </si>
+  <si>
+    <t>but we now need to process any SEND sensor messages from ACCESP.</t>
+  </si>
+  <si>
+    <t>void nsWiThrottle::relayLocoNetMessage(std::string s) {</t>
+  </si>
+  <si>
+    <t>needs a re-write because we prefix the payload with RECEIVE.  Instead we should just send the same</t>
+  </si>
+  <si>
+    <t>loconet over tcp message</t>
+  </si>
+  <si>
+    <t>Testing with T 192.168.1.104</t>
+  </si>
+  <si>
+    <t>and P 2560</t>
+  </si>
+  <si>
+    <t>The client is connected directly to DCC_ESP and not into JMRI</t>
+  </si>
+  <si>
+    <t>Turnout tests.</t>
+  </si>
+  <si>
+    <t>1/ From JMRI</t>
+  </si>
+  <si>
+    <t>IN: RECEIVE B0 01 30 7E</t>
+  </si>
+  <si>
+    <t>Turnout 2 closed</t>
+  </si>
+  <si>
+    <t>address 2 closed</t>
+  </si>
+  <si>
+    <t>seen on ACC serial</t>
+  </si>
+  <si>
+    <t>so this works.</t>
+  </si>
+  <si>
+    <t>But, the htm pages seem to have slowed down.</t>
+  </si>
+  <si>
+    <t>2/ From turnout.htm</t>
+  </si>
+  <si>
+    <t>works, see the commands flowing out to serial.</t>
+  </si>
+  <si>
+    <t>MAS tests</t>
+  </si>
+  <si>
+    <t>[ED 0B 7F 32 01 0E 75 06 00 00 28]  Extended Accessory Decoder Set Digitrax Address 59 (NMRA Address 55) to Aspect 6.</t>
+  </si>
+  <si>
+    <t>[ED 0B 7F 32 01 0E 75 15 00 00 3B]  Extended Accessory Decoder Set Digitrax Address 59 (NMRA Address 55) to Aspect 21.</t>
+  </si>
+  <si>
+    <t>[ED 0B 7F 32 01 0E 75 09 00 00 27]  Extended Accessory Decoder Set Digitrax Address 59 (NMRA Address 55) to Aspect 9.</t>
+  </si>
+  <si>
+    <t>Does not work.  Don't see any messages coming out of port 2560 in ACCESP mode.</t>
+  </si>
+  <si>
+    <t>now try debug mode</t>
+  </si>
+  <si>
+    <t>[ED 0B 7F 32 01 0E 75 07 00 00 29]  Extended Accessory Decoder Set Digitrax Address 59 (NMRA Address 55) to Aspect 7.</t>
+  </si>
+  <si>
+    <t>[ED 0B 7F 32 01 0E 75 08 00 00 26]  Extended Accessory Decoder Set Digitrax Address 59 (NMRA Address 55) to Aspect 8.</t>
+  </si>
+  <si>
+    <t>RECEIVE ED 0B 7F 32 01 0E 75 06 00 00 28</t>
+  </si>
+  <si>
+    <t>RECEIVE 0xB4 0x7D 0x7F 0x49</t>
+  </si>
+  <si>
+    <t>RECEIVE ED 0B 7F 32 01 0E 75 07 00 00 29</t>
+  </si>
+  <si>
+    <t>RECEIVE ED 0B 7F 32 01 0E 75 08 00 00 26</t>
+  </si>
+  <si>
+    <t>&lt;&lt;&lt; what is this message?</t>
+  </si>
+  <si>
+    <t>MAS test - put ACCESP on JMRI server</t>
+  </si>
+  <si>
+    <t>IN: RECEIVE ED 0B 7F 32 01 0E 75 05 00 00 2B</t>
+  </si>
+  <si>
+    <t>MAS 59 05</t>
+  </si>
+  <si>
+    <t>IN: RECEIVE ED 0B 7F 32 01 0E 75 06 00 00 28</t>
+  </si>
+  <si>
+    <t>MAS 59 06</t>
+  </si>
+  <si>
+    <t>IN: RECEIVE ED 0B 7F 32 01 0E 75 07 00 00 29</t>
+  </si>
+  <si>
+    <t>MAS 59 07</t>
+  </si>
+  <si>
+    <t>TCP .102:4234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">this works, because it is seeing the RECEIVE message ED 0B </t>
+  </si>
+  <si>
+    <t>So for MAS, we need to treat direct ACC_ESP clients differently, we need to</t>
+  </si>
+  <si>
+    <t>relay the ED 0B message to them, as they won't react to the B4 message.</t>
+  </si>
+  <si>
+    <t>SENSOR tests</t>
+  </si>
+  <si>
+    <t>ACC_ESP into JMRI works.</t>
+  </si>
+  <si>
+    <t>ACC_ESP direct into DCC_ESP</t>
+  </si>
+  <si>
+    <t>Does not work.</t>
+  </si>
+  <si>
+    <t>Hercules on port 2560</t>
+  </si>
+  <si>
+    <t>nothing is echoed over port 4234</t>
+  </si>
+  <si>
+    <t>Hercules on port 4234</t>
+  </si>
+  <si>
+    <t>For a sensor to report, it has to iniate with SEND</t>
+  </si>
+  <si>
+    <t>The issue here, is the DCC_ESP consumes the sensor event</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and responds to JRMI (and all clients) with RECEIVE.  </t>
+  </si>
+  <si>
+    <t>JRMI needs to see a SEND report.</t>
+  </si>
+  <si>
+    <t>Need to figure out what we want.</t>
+  </si>
+  <si>
+    <t>For a non JMRI-laptop system, you can run ACC_ESP as a LN server.  It only needs to support turnouts because DCC_ESP cannot control MAS or support sensors.</t>
+  </si>
+  <si>
+    <t>If JRMI is in the system</t>
+  </si>
+  <si>
+    <t>You can also acc ACC_ESP as clients and again these will support turnouts only, but there is a max limit of 8 clients for all connected throttles and accessory clients.</t>
+  </si>
+  <si>
+    <t>there is really no point direct connecting ACC_ESP to DCC_ESP</t>
+  </si>
+  <si>
+    <t>it will only support turnout messages, not sensors nor MAS.</t>
+  </si>
+  <si>
+    <t>LAST TESTS.  ACC_ESP running as LN, no JMRI in the system.</t>
+  </si>
+  <si>
+    <t>The turnout messages work as we expect, the ACC_ESP_master is reacting to turnout changes on turnout.htm</t>
+  </si>
+  <si>
+    <t>and I assume any second or third ACC_ESP client will also process these correctly.</t>
+  </si>
+  <si>
+    <t>Hence you can build a stand-alone turnout only arrangement without JMRI being in the loop and run it all over Wifi.</t>
+  </si>
+  <si>
+    <t>BUT there was also another option.  ACC_ESP and laptop only, no need for a DCC_ESP device.</t>
+  </si>
+  <si>
+    <t>here you can drive sensors, turnouts and Mas into JMRI and operate independently of your DCC command station.</t>
+  </si>
+  <si>
+    <t>DCC_ESP is LN server, no JMRI, ACC_ESP as clients, no building Wifi</t>
+  </si>
+  <si>
+    <t>As above, but using building Wifi</t>
+  </si>
+  <si>
+    <t>JRMI, no buildig wifi, no DCC controller, working in to ACC_ESP wifi running as LN server</t>
+  </si>
+  <si>
+    <t>As 3 but using building wifi</t>
+  </si>
+  <si>
+    <t>can also add clients to JMRI LN server</t>
+  </si>
+  <si>
+    <t>DCC_ESP as Wifi as LN controller with JMRI laptop connected</t>
+  </si>
+  <si>
+    <t>and ACC_ESP clients connected to laptop JRMI server</t>
+  </si>
+  <si>
+    <t>Same as 5 but using building Wifi</t>
+  </si>
+  <si>
+    <t>and ACC_ESP clients connected to DCC_ESP</t>
+  </si>
+  <si>
+    <t>as 7 but over building Wifi.</t>
+  </si>
+  <si>
+    <t>with ACC_ESP clients</t>
+  </si>
+  <si>
+    <t>That’s a silly number of options</t>
+  </si>
+  <si>
+    <t>normally you'd use buildingn wifi, DCC_ESP as a controller and ACC_ESP into the JMRI server.</t>
+  </si>
+  <si>
+    <t>which is option 5</t>
+  </si>
+  <si>
+    <t>can also add clients to JMRI LN server (can you?  They are wifi clients of the ACC_ESP_LN but I guess they can connect to the laptop IP)</t>
+  </si>
+  <si>
+    <t>===========================================================================</t>
+  </si>
+  <si>
+    <t>What does JMRI need to see?</t>
+  </si>
+  <si>
+    <t>JMRI and ACC_ESP clients are almost the same thing…but not quite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and it responds to unsolicited turnout messages </t>
+  </si>
+  <si>
+    <t>T77 thrown</t>
+  </si>
+  <si>
+    <t>T77 closed</t>
+  </si>
+  <si>
+    <t>B0 4C 30 33</t>
+  </si>
+  <si>
+    <t>B0 4C 10 13</t>
+  </si>
+  <si>
+    <t>port 2560</t>
+  </si>
+  <si>
+    <t>port 4234</t>
+  </si>
+  <si>
+    <t>SEND B0 4C 10 13</t>
+  </si>
+  <si>
+    <t>from DCC_ESP</t>
+  </si>
+  <si>
+    <t>from ACC_ESP into</t>
+  </si>
+  <si>
+    <t>DCC_ESP:2560</t>
+  </si>
+  <si>
+    <t>neither send or receive does anything</t>
+  </si>
+  <si>
+    <t>RECEIVE B0 4C 10 13</t>
+  </si>
+  <si>
+    <t>&lt;&lt; RECEIVE payload</t>
+  </si>
+  <si>
+    <t>&lt;&lt;RECEIVE payload</t>
+  </si>
+  <si>
+    <t>JMRI port 2560 (i.e. into DCC controller) characterisation</t>
+  </si>
+  <si>
+    <t>JMRI server port 4234 characterisation (i.e. relays these messages to DCC_ESP controller)</t>
+  </si>
+  <si>
+    <t>&lt;&lt;RECEIVE B2 1B 40 16  sensor 55 low</t>
+  </si>
+  <si>
+    <t>&lt;&lt;RECEIVE B0 4C 10 13</t>
+  </si>
+  <si>
+    <t>commands coming from JMRI and appearing at ACC_ESP</t>
+  </si>
+  <si>
+    <t>VERSION JMRI Server 5.16+R909e15189e</t>
+  </si>
+  <si>
+    <t>RECEIVE B0 4C 00 03</t>
+  </si>
+  <si>
+    <t>JMRI server expects no response in return.</t>
+  </si>
+  <si>
+    <t>SEND B2 1B 40 16</t>
+  </si>
+  <si>
+    <t>RECEIVE B2 1B 40 16</t>
+  </si>
+  <si>
+    <t>and unsolicited turnout commands are</t>
+  </si>
+  <si>
+    <t>ACC_ESP can raise sensor events</t>
+  </si>
+  <si>
+    <t>in which case it could toggle a turnout and thus need to send its status</t>
+  </si>
+  <si>
+    <t>RECEIVE B0 36 10 69</t>
+  </si>
+  <si>
+    <t>turnout commands processed on DCC_ESP appear as receive messages on port 4234</t>
+  </si>
+  <si>
+    <t>sensor queries appear thus (assuming DCC_ESP does not home that sensor and thus respond by modifying the payload)</t>
+  </si>
+  <si>
+    <t>RECEIVE B2 1B 50 06</t>
+  </si>
+  <si>
+    <t>effectively this is a poll to sensor 55, or this is DCC_ESP reporting a sensor event</t>
+  </si>
+  <si>
+    <t>ACC_ESP is really a consumer of turnout commands (i.e. RECEIVE), not a generator, but ultimately one might add local pushbuttons to it</t>
+  </si>
+  <si>
+    <t>Note:  when ACC_ESP is running as a client, it only responds to incoming RECEIVE messages.  It can raise SEND for sensors and turnouts.</t>
+  </si>
+  <si>
+    <t>when ACC_ESP is running as a server (LN controller), it expects to see the full TCP-wrapper SEND,RECEIVE,SENT OK</t>
+  </si>
+  <si>
+    <t>AT present, if you connect ACC_ESP as a client to ECC_ESP on port 2560, then it does the following;</t>
+  </si>
+  <si>
+    <t>DCC_ESP thinks it is another LN client, even though it can be promoted to ACCESP due to its ping messages</t>
+  </si>
+  <si>
+    <t>ACC_ESP will see the RECEIVE messages generated by DCC_ESP as it responds to JMRI Panel Pro, and so it is able to slave itself to turnout commands</t>
+  </si>
+  <si>
+    <t>hmm, not sure…..</t>
+  </si>
+  <si>
+    <t>I think for now we leave as is, and focus on the 4234 port functions.</t>
+  </si>
+  <si>
+    <t>this is the serial monitor on ACC_ESP</t>
+  </si>
+  <si>
+    <t>it raises an event as a SEND message and sees this come back as RECEIVE. Followed by SENT OK</t>
+  </si>
+  <si>
+    <t>what If JMRI PP polls the sensor?</t>
+  </si>
+  <si>
+    <t>DCC_ESP processes the message which ultimately results in a RECEIVE being sent to all 4234 clients</t>
+  </si>
+  <si>
+    <t>this triggers a poll on the ACC_ESP</t>
+  </si>
+  <si>
+    <t>the ACC_ESP sends this to port 4234</t>
+  </si>
+  <si>
+    <t>and this results in an echo of the updated sensor state 70 in this case.</t>
+  </si>
+  <si>
+    <t>sent ok is generated by the DCC_ESP and not by Panel Pro (because PP is not a loconet processor it is a client)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The thing that puzzles me is I expect that second IN RECEIVE to trigger a </t>
+  </si>
+  <si>
+    <t>loop condition but it does not.  No qry sensor  event is kicked off</t>
+  </si>
+  <si>
+    <t>I am not complaining but I cannot explain it.</t>
+  </si>
+  <si>
+    <t>Need to run a test where we have a ACC_ESP acting as a Loconet server and a second ACC_ESP acting as a client to port 4234</t>
+  </si>
+  <si>
+    <t>this system is entirely independent of a DCC controller, and can be used to as a standalone Panel Pro and turnouts/sensor system.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -492,13 +1178,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -513,10 +1213,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -578,6 +1280,95 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>68580</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1F6CCFA-2B94-C327-158D-297621B752A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7993380" y="17907000"/>
+          <a:ext cx="5021580" cy="2293620"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-AU" sz="1100"/>
+            <a:t>hardware call.  Add the 2560 WiT</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-AU" sz="1100" baseline="0"/>
+            <a:t> port.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-AU" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-AU" sz="1100" baseline="0"/>
+            <a:t>also add a flag to show we have on LN connection, i.e. JMRI laptop is active.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-AU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -846,10 +1637,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:P202"/>
+  <dimension ref="B2:T284"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.5546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1669,38 +2461,1586 @@
         <v>140</v>
       </c>
     </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B193" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B198" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B199" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B200" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B201" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B202" t="s">
         <v>118</v>
+      </c>
+    </row>
+    <row r="207" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B207" s="1">
+        <v>46246</v>
+      </c>
+      <c r="C207" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="208" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B208" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="210" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B210" t="s">
+        <v>152</v>
+      </c>
+      <c r="E210" t="s">
+        <v>164</v>
+      </c>
+      <c r="G210" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="211" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B211" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="212" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B212" t="s">
+        <v>154</v>
+      </c>
+      <c r="H212" t="s">
+        <v>157</v>
+      </c>
+      <c r="M212" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q212" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="213" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B213" t="s">
+        <v>155</v>
+      </c>
+      <c r="H213" t="s">
+        <v>158</v>
+      </c>
+      <c r="M213" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q213" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="214" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B214" t="s">
+        <v>156</v>
+      </c>
+      <c r="H214" t="s">
+        <v>159</v>
+      </c>
+      <c r="M214" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q214" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="215" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M215" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q215" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="216" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M216" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="217" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M217" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="218" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M218" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="220" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B220" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="221" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M221" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q221" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="222" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M222" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q222" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="223" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M223" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="224" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M224" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="225" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B225" t="s">
+        <v>51</v>
+      </c>
+      <c r="H225" t="s">
+        <v>177</v>
+      </c>
+      <c r="M225" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="226" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B226" t="s">
+        <v>52</v>
+      </c>
+      <c r="H226" t="s">
+        <v>178</v>
+      </c>
+      <c r="M226" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="227" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="M227" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="228" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="M228" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="229" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="M229" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="230" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="M230" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="232" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B232" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="233" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B233" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q233" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="234" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B234" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q234" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="235" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="Q235" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="236" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="G236" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="237" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="G237" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q237" t="s">
+        <v>38</v>
+      </c>
+      <c r="T237" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="238" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B238" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q238" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T238" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="239" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="Q239" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="240" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B240" t="s">
+        <v>52</v>
+      </c>
+      <c r="O240" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q240" t="s">
+        <v>19</v>
+      </c>
+      <c r="T240" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="242" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B242" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="243" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B243" t="s">
+        <v>51</v>
+      </c>
+      <c r="G243" t="s">
+        <v>189</v>
+      </c>
+      <c r="L243" t="s">
+        <v>190</v>
+      </c>
+      <c r="M243" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q243" t="s">
+        <v>39</v>
+      </c>
+      <c r="S243" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="244" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B244" t="s">
+        <v>52</v>
+      </c>
+      <c r="G244" t="s">
+        <v>191</v>
+      </c>
+      <c r="M244" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="245" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="M245" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="246" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="G246" t="s">
+        <v>192</v>
+      </c>
+      <c r="M246" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="247" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="G247" t="s">
+        <v>193</v>
+      </c>
+      <c r="M247" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q247" t="s">
+        <v>19</v>
+      </c>
+      <c r="S247" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="248" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="G248" t="s">
+        <v>194</v>
+      </c>
+      <c r="M248" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="252" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="M252" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="253" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="Q253" t="s">
+        <v>133</v>
+      </c>
+      <c r="T253" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="254" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="Q254" t="s">
+        <v>19</v>
+      </c>
+      <c r="T254" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="255" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="Q255" t="s">
+        <v>40</v>
+      </c>
+      <c r="T255" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="256" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="M256" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q256" t="s">
+        <v>19</v>
+      </c>
+      <c r="T256" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="257" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="M257" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="258" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="M258" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="259" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="H259" t="s">
+        <v>203</v>
+      </c>
+      <c r="L259" t="s">
+        <v>202</v>
+      </c>
+      <c r="M259" t="s">
+        <v>174</v>
+      </c>
+      <c r="P259" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="260" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="H260" t="s">
+        <v>204</v>
+      </c>
+      <c r="M260" t="s">
+        <v>175</v>
+      </c>
+      <c r="P260" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="261" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="H261" t="s">
+        <v>204</v>
+      </c>
+      <c r="M261" t="s">
+        <v>40</v>
+      </c>
+      <c r="P261" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="265" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B265" t="s">
+        <v>212</v>
+      </c>
+      <c r="M265" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="266" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="M266" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="267" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="M267" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="268" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="N268" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="270" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B270" t="s">
+        <v>215</v>
+      </c>
+      <c r="M270" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="271" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="M271" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="272" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="M272" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="275" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B275" t="s">
+        <v>217</v>
+      </c>
+      <c r="C275" s="1">
+        <v>46246</v>
+      </c>
+    </row>
+    <row r="276" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B276" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="277" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B277" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="278" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B278" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="280" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B280" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="281" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B281" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="282" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B282" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="283" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B283" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="284" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B284" t="s">
+        <v>225</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82C5BB75-4847-4E5A-B666-5580DC8B8281}">
+  <dimension ref="B2:Y84"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B2" s="1">
+        <v>46250</v>
+      </c>
+      <c r="D2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="3" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B3" s="4" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="4" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="5" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="6" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="D6" t="s">
+        <v>228</v>
+      </c>
+      <c r="J6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="7" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="D7" t="s">
+        <v>229</v>
+      </c>
+      <c r="J7" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="9" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="10" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>334</v>
+      </c>
+      <c r="J10" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="11" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="D11" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="12" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="S12" t="s">
+        <v>329</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="13" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>321</v>
+      </c>
+      <c r="S13" t="s">
+        <v>326</v>
+      </c>
+      <c r="V13" t="s">
+        <v>327</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="14" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="D14" t="s">
+        <v>335</v>
+      </c>
+      <c r="N14" t="s">
+        <v>322</v>
+      </c>
+      <c r="P14" t="s">
+        <v>325</v>
+      </c>
+      <c r="S14" t="s">
+        <v>333</v>
+      </c>
+      <c r="V14" t="s">
+        <v>328</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="15" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="D15" t="s">
+        <v>339</v>
+      </c>
+      <c r="N15" t="s">
+        <v>323</v>
+      </c>
+      <c r="P15" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B18" s="4" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C21" t="s">
+        <v>190</v>
+      </c>
+      <c r="D21" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C22" t="s">
+        <v>190</v>
+      </c>
+      <c r="D22" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D23" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="D24" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C26" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C27" t="s">
+        <v>190</v>
+      </c>
+      <c r="D27" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C29" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C30" t="s">
+        <v>190</v>
+      </c>
+      <c r="D30" t="s">
+        <v>352</v>
+      </c>
+      <c r="G30" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>230</v>
+      </c>
+      <c r="H32" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C33" t="s">
+        <v>202</v>
+      </c>
+      <c r="D33" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C34" t="s">
+        <v>190</v>
+      </c>
+      <c r="D34" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C35" t="s">
+        <v>190</v>
+      </c>
+      <c r="D35" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>346</v>
+      </c>
+      <c r="H37" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C38" t="s">
+        <v>202</v>
+      </c>
+      <c r="D38" t="s">
+        <v>328</v>
+      </c>
+      <c r="H38" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C39" t="s">
+        <v>190</v>
+      </c>
+      <c r="D39" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C40" t="s">
+        <v>190</v>
+      </c>
+      <c r="D40" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="D42" t="s">
+        <v>176</v>
+      </c>
+      <c r="G42" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="D43" t="s">
+        <v>126</v>
+      </c>
+      <c r="G43" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="D44" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="D45" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="D46" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="D47" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="D48" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="D49" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="50" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="D50" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="D52" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="53" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="C53" t="s">
+        <v>190</v>
+      </c>
+      <c r="D53" t="s">
+        <v>173</v>
+      </c>
+      <c r="H53" t="s">
+        <v>365</v>
+      </c>
+      <c r="T53" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="54" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="D54" t="s">
+        <v>43</v>
+      </c>
+      <c r="H54" t="s">
+        <v>366</v>
+      </c>
+      <c r="T54" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="55" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="D55" t="s">
+        <v>44</v>
+      </c>
+      <c r="T55" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="56" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="C56" t="s">
+        <v>202</v>
+      </c>
+      <c r="D56" t="s">
+        <v>174</v>
+      </c>
+      <c r="H56" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="57" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="C57" t="s">
+        <v>190</v>
+      </c>
+      <c r="D57" t="s">
+        <v>175</v>
+      </c>
+      <c r="H57" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="58" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="C58" t="s">
+        <v>190</v>
+      </c>
+      <c r="D58" t="s">
+        <v>40</v>
+      </c>
+      <c r="H58" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="60" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B60" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="61" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B61" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="63" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B63" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="64" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="C64" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C65" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C66" t="s">
+        <v>360</v>
+      </c>
+      <c r="F66" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="68" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B68" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B69" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B70" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="72" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B72" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="74" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B74" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="75" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B75" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="77" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B77" t="s">
+        <v>240</v>
+      </c>
+      <c r="H77" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="78" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H78" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B81" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B82" s="1">
+        <v>46263</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B84" t="s">
+        <v>319</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA93CE79-A0A0-4623-B7EC-2526B7B16DB8}">
+  <dimension ref="B2:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>374</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E127FB4C-33E7-4FE2-8B24-29A0A49C7025}">
+  <dimension ref="B2:K111"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>248</v>
+      </c>
+      <c r="E10" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>248</v>
+      </c>
+      <c r="E13" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>264</v>
+      </c>
+      <c r="K36" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="K37" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
+        <v>265</v>
+      </c>
+      <c r="F39" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B40" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B42" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B43" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B44" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B46" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B47" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B52" t="s">
+        <v>269</v>
+      </c>
+      <c r="G52" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B53" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B54" t="s">
+        <v>271</v>
+      </c>
+      <c r="H54" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B55" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B56" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B57" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B58" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B59" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B60" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B61" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B62" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B63" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B68" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="69" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B69" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B70" t="s">
+        <v>283</v>
+      </c>
+      <c r="G70" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B71" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B72" t="s">
+        <v>44</v>
+      </c>
+      <c r="G72" t="s">
+        <v>39</v>
+      </c>
+      <c r="K72" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B73" t="s">
+        <v>174</v>
+      </c>
+      <c r="K73" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B74" t="s">
+        <v>175</v>
+      </c>
+      <c r="G74" t="s">
+        <v>40</v>
+      </c>
+      <c r="K74" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="75" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="G75" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="G77" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="C79" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="81" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B81" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="G82" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B83" t="s">
+        <v>126</v>
+      </c>
+      <c r="G83" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B84" t="s">
+        <v>172</v>
+      </c>
+      <c r="G84" t="s">
+        <v>19</v>
+      </c>
+      <c r="K84" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B85" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B86" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B87" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B88" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B89" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="90" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B90" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="91" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B91" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="94" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B94" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B95" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B96" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B98" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B99" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B100" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B105" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B106" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B107" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B108" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B110" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B111" t="s">
+        <v>302</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{742A0ACD-6174-4B2C-8FA8-5AD79CCAEE95}">
+  <dimension ref="B3:M22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="D11" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>308</v>
+      </c>
+      <c r="M13" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="D14" t="s">
+        <v>309</v>
+      </c>
+      <c r="M14" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="M15" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D22" t="s">
+        <v>313</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>